--- a/excel-files/TAGUIG_PATEROS/NAPINDAN INTEGRATED SCHOOL.xlsx
+++ b/excel-files/TAGUIG_PATEROS/NAPINDAN INTEGRATED SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7374784F-51F1-4721-8F65-3BFA3C64F25D}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03FD681E-236F-454A-A377-2F05D6FEC08A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -650,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -784,6 +784,19 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3495,7 +3508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3507,7 +3520,7 @@
     <col min="9" max="12" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:18" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3532,8 +3545,18 @@
       <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+    </row>
+    <row r="2" spans="1:18" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3546,7 +3569,7 @@
       <c r="D2" s="42">
         <v>601</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="48">
         <v>2024</v>
       </c>
       <c r="F2" s="43" t="s">
@@ -3561,7 +3584,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+    <row r="3" spans="1:18" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3570,7 +3593,7 @@
       </c>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="48" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="43" t="s">
@@ -3585,7 +3608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+    <row r="4" spans="1:18" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3598,7 +3621,7 @@
       <c r="D4" s="42">
         <v>601</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="48">
         <v>2024</v>
       </c>
       <c r="F4" s="43" t="s">
@@ -3613,7 +3636,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+    <row r="5" spans="1:18" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3626,7 +3649,7 @@
       <c r="D5" s="42">
         <v>601</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="48">
         <v>2025</v>
       </c>
       <c r="F5" s="43" t="s">
@@ -3641,7 +3664,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:18" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3661,12 +3684,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:18">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+      <c r="E7" s="51"/>
+    </row>
+    <row r="8" spans="1:18" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3687,8 +3710,9 @@
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+      <c r="R8" s="50"/>
+    </row>
+    <row r="9" spans="1:18" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3710,7 +3734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:18" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3732,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:18" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3754,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="24" customHeight="1">
+    <row r="12" spans="1:18" ht="24" customHeight="1">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3782,7 +3806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="19.5">
+    <row r="13" spans="1:18" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -3804,12 +3828,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:18">
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" ht="49.5" customHeight="1">
+      <c r="E14" s="51"/>
+    </row>
+    <row r="15" spans="1:18" ht="49.5" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3829,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="29.25" customHeight="1">
+    <row r="16" spans="1:18" ht="29.25" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3909,7 +3933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="19.149999999999999">
+    <row r="20" spans="1:8" ht="19.5">
       <c r="A20" s="1">
         <v>3</v>
       </c>
@@ -3934,7 +3958,7 @@
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="E21" s="52"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -3972,7 +3996,7 @@
       <c r="D23" s="42">
         <v>660</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="48">
         <v>2024</v>
       </c>
       <c r="F23" s="43" t="s">
@@ -4000,7 +4024,7 @@
       <c r="D24" s="42">
         <v>692</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="48">
         <v>2025</v>
       </c>
       <c r="F24" s="43" t="s">
@@ -4028,7 +4052,7 @@
       <c r="D25" s="42">
         <v>704</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E25" s="48">
         <v>2024</v>
       </c>
       <c r="F25" s="43" t="s">
@@ -4056,7 +4080,7 @@
       <c r="D26" s="42">
         <v>692</v>
       </c>
-      <c r="E26" s="42">
+      <c r="E26" s="48">
         <v>2024</v>
       </c>
       <c r="F26" s="43" t="s">
@@ -4084,7 +4108,7 @@
       <c r="D27" s="42">
         <v>692</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E27" s="48">
         <v>2024</v>
       </c>
       <c r="F27" s="43" t="s">
@@ -4112,7 +4136,7 @@
       <c r="D28" s="42">
         <v>692</v>
       </c>
-      <c r="E28" s="42">
+      <c r="E28" s="48">
         <v>2024</v>
       </c>
       <c r="F28" s="43" t="s">
@@ -4172,7 +4196,7 @@
       <c r="B31" s="7"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="E31" s="52"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -4362,7 +4386,7 @@
       <c r="B41" s="7"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
+      <c r="E41" s="52"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -4552,7 +4576,7 @@
       <c r="B51" s="7"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
+      <c r="E51" s="52"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -4796,7 +4820,7 @@
       <c r="B61" s="7"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
+      <c r="E61" s="52"/>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
@@ -5002,7 +5026,7 @@
       <c r="B71" s="7"/>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
+      <c r="E71" s="49"/>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -5194,7 +5218,7 @@
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
+      <c r="E81" s="49"/>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
@@ -5386,7 +5410,7 @@
       <c r="B91" s="7"/>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
+      <c r="E91" s="49"/>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
@@ -5558,11 +5582,11 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15:E20 E6 E32:E40 E92:E99 E62:E70 E42:E50 E52:E60 E72:E80 E82:E90 E8:E13 E22 E29:E30" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F20 F6 F32:F40 F42:F50 F92:F99 F62:F70 F72:F80 F82:F90 F52:F60 F8:F13 F22 F29:F30" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R8 E92:E99 E82:E90 E72:E80 E62:E70 E52:E60 E42:E50 E32:E40 E22:E30 E15:E20 E8:E13 E2:E6" xr:uid="{60F0DBD4-8B12-4C51-B7FC-405A0B50221F}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5574,7 +5598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13978,186 +14002,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C63:C71" name="Textbooks"/>
@@ -14175,8 +14019,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F14:F21 F33:F41 F23:F31 X112:X127 F43:F51 F53:F61 F5:F12 F83:F91 F93:F101 F63:F71 F103:F110 R103:R110 L103:L110 X103:X110 F73:F81" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G63:G71 G14:G21 G33:G41 G23:G31 G53:G61 G103:G110 G43:G51 G83:G91 G93:G101 G73:G81" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -22937,188 +22781,8 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="1:28">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10" ht="15"/>
-    <row r="170" spans="10:10" ht="15"/>
+    <row r="169" ht="15"/>
+    <row r="170" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C113:C120 C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C77:C87 C89:C99 C101:C111 C67:C75" name="Textbooks"/>
@@ -23138,8 +22802,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S113:S120 Y113:Y120 G113:G120 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 Y101:Y111 S55:S65 M113:M120 M55:M65 S77:S87 M77:M87 G77:G87 Y77:Y87 Y55:Y65 Y89:Y99 M89:M99 G101:G111 G55:G65 G67:G75 S101:S111 M101:M111 S89:S99 S67:S75 Y67:Y75 M67:M75 G89:G99" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X77:X87 R55:R65 X55:X65 F67:F75 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L77:L87 L55:L65 L89:L99 L101:L111 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R77:R87 F55:F65 X89:X99 R101:R111 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F77:F87 X101:X111 F3:F10 F101:F111 X113:X120 F12:F19 F113:F120 R113:R120 L113:L120 R89:R99 X67:X75 R67:R75 L67:L75 F89:F99" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F113:F120 F101:F111 F89:F99 F77:F87 F67:F75 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L113:L120 L101:L111 L89:L99 L77:L87 L67:L75 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R113:R120 R101:R111 R89:R99 R77:R87 R67:R75 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X113:X120 X101:X111 X89:X99 X77:X87 X67:X75 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
